--- a/artfynd/A 35260-2025 artfynd.xlsx
+++ b/artfynd/A 35260-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128261988</v>
       </c>
       <c r="B2" t="n">
-        <v>92287</v>
+        <v>92295</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128261987</v>
       </c>
       <c r="B3" t="n">
-        <v>92287</v>
+        <v>92295</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35260-2025 artfynd.xlsx
+++ b/artfynd/A 35260-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128261988</v>
       </c>
       <c r="B2" t="n">
-        <v>92295</v>
+        <v>92387</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128261987</v>
       </c>
       <c r="B3" t="n">
-        <v>92295</v>
+        <v>92387</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35260-2025 artfynd.xlsx
+++ b/artfynd/A 35260-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128261988</v>
       </c>
       <c r="B2" t="n">
-        <v>92387</v>
+        <v>92399</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128261987</v>
       </c>
       <c r="B3" t="n">
-        <v>92387</v>
+        <v>92399</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35260-2025 artfynd.xlsx
+++ b/artfynd/A 35260-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128261988</v>
       </c>
       <c r="B2" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128261987</v>
       </c>
       <c r="B3" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35260-2025 artfynd.xlsx
+++ b/artfynd/A 35260-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128261988</v>
       </c>
       <c r="B2" t="n">
-        <v>92401</v>
+        <v>92402</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128261987</v>
       </c>
       <c r="B3" t="n">
-        <v>92401</v>
+        <v>92402</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35260-2025 artfynd.xlsx
+++ b/artfynd/A 35260-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128261988</v>
       </c>
       <c r="B2" t="n">
-        <v>92402</v>
+        <v>92429</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128261987</v>
       </c>
       <c r="B3" t="n">
-        <v>92402</v>
+        <v>92429</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35260-2025 artfynd.xlsx
+++ b/artfynd/A 35260-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128261988</v>
       </c>
       <c r="B2" t="n">
-        <v>92429</v>
+        <v>92439</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128261987</v>
       </c>
       <c r="B3" t="n">
-        <v>92429</v>
+        <v>92439</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35260-2025 artfynd.xlsx
+++ b/artfynd/A 35260-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128261988</v>
+        <v>128261987</v>
       </c>
       <c r="B2" t="n">
-        <v>92439</v>
+        <v>92869</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>671922</v>
+        <v>671861</v>
       </c>
       <c r="R2" t="n">
-        <v>6648158</v>
+        <v>6648177</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128261987</v>
+        <v>128261988</v>
       </c>
       <c r="B3" t="n">
-        <v>92439</v>
+        <v>92869</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>671861</v>
+        <v>671922</v>
       </c>
       <c r="R3" t="n">
-        <v>6648177</v>
+        <v>6648158</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -866,6 +866,103 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128262008</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91443</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5754</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gultoppig fingersvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Ramaria testaceoflava</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>671851</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6648067</v>
+      </c>
+      <c r="S4" t="n">
+        <v>20</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
